--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse; encounter reference; Provenance</t>
+          <t xml:space="preserve">QuestionnaireResponse; Provenance</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation (derived risk tier)</t>
+          <t xml:space="preserve">Observation</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flag (suicide screening status)</t>
+          <t xml:space="preserve">Flag</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2C</t>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task (role-routed); ServiceRequest (BH consult / BSSA); PlanDefinition reference</t>
+          <t xml:space="preserve">Task; ServiceRequest; PlanDefinition</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task (mitigation checklist); Procedure (patient relocation)</t>
+          <t xml:space="preserve">Task; Procedure</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1B</t>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ServiceRequest (suicide precautions, observation level); required signature</t>
+          <t xml:space="preserve">ServiceRequest</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation (room clearance result); List (belongings inventory)</t>
+          <t xml:space="preserve">Observation; List</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1D</t>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation series (time-stamped observations); CareTeam (observer assignment)</t>
+          <t xml:space="preserve">Observation; CareTeam</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flag (active precautions); current parameters</t>
+          <t xml:space="preserve">Flag</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse (BSSA)</t>
+          <t xml:space="preserve">QuestionnaireResponse</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation (BSSA outcome); Task (next-step routing); Flag (cannot leave until evaluated)</t>
+          <t xml:space="preserve">Observation; Task; Flag</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse (C-SSRS Full; SAFE-T framing)</t>
+          <t xml:space="preserve">QuestionnaireResponse</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="74" customHeight="1">
+    <row r="15" ht="46" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-1B</t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation (current suicide risk level); Condition (suicide-risk condition, coded); Flag (longitudinal risk indicator)</t>
+          <t xml:space="preserve">Observation; Condition; Flag</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task series; restriction.period; PlanDefinition (reassessment cadence)</t>
+          <t xml:space="preserve">Task; PlanDefinition</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation (updated risk); ServiceRequest (updated precautions); prior-value preservation</t>
+          <t xml:space="preserve">Observation; ServiceRequest</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">New instance of Room Clearance Checklist (11.3-1C); updated CareTeam for observer handoff</t>
+          <t xml:space="preserve">CareTeam</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1A</t>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse (Stanley-Brown safety plan); CarePlan</t>
+          <t xml:space="preserve">QuestionnaireResponse; CarePlan</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1B</t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CarePlan; version history; Provenance for each version</t>
+          <t xml:space="preserve">CarePlan; Provenance</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="74" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2A</t>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedure (lethal means counseling delivered); CarePlan.activity (means-safety actions, who/what/when/where)</t>
+          <t xml:space="preserve">Procedure; CarePlan</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2B</t>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task (discharge readiness); Flag (blocking alert if incomplete)</t>
+          <t xml:space="preserve">Task; Flag</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="74" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-3A</t>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Composition (after-visit summary); DocumentReference (printed/portal-delivered safety plan; discharge instructions)</t>
+          <t xml:space="preserve">Composition; DocumentReference</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="74" customHeight="1">
+    <row r="24" ht="46" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-1A</t>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ServiceRequest (urgent outpatient referral); Appointment request; Communication to receiving provider</t>
+          <t xml:space="preserve">ServiceRequest; Appointment; Communication</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="46" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-1B</t>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bundle (transition-of-care packet); Composition; Provenance for delivery acknowledgement</t>
+          <t xml:space="preserve">Bundle; Composition; Provenance</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task series (24–48h call, 7-day visit); CommunicationRequest; Communication (per-attempt outreach); PlanDefinition (follow-up cadence); registry enrollment</t>
+          <t xml:space="preserve">Task; CommunicationRequest; Communication; PlanDefinition</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2B</t>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication (outreach attempt); updated Observation (current risk); updated CarePlan</t>
+          <t xml:space="preserve">Communication; Observation; CarePlan</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="74" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2C</t>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Task status transitions to overdue; Communication (supervisor alert); Flag (escalated follow-up status)</t>
+          <t xml:space="preserve">Task; Communication; Flag</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -245,1093 +245,1513 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">11.2-1C (proposed)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient (or caregiver)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respondent</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete a self-administered suicide risk screener on a patient-facing device</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Age-appropriate screening instrument; a private space and device (tablet, kiosk, or portal); language and reading-level preference; interpreter when needed; whether a support person is present</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionnaireResponse authored by the patient (author and source = Patient); language used; whether the patient answered privately; interpreter identity when one was used</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The patient completes the screener directly; the EHR records the patient rather than the nurse as author, notes whether anyone else was present, and routes the result into the same classification path as a staff-administered screen</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments; DC.3.2 Support Patient Education and Self-Care</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="88" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.2-1D (proposed)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triage Nurse</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screener</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Document a declined, deferred, or incompletable screen</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason the screen did not happen (patient declines, altered mental status, intoxication, acute medical instability, communication barrier); local policy on when to re-attempt</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discrete "screening not performed" record with a coded reason; re-attempt Task with a due time; metadata supporting measure exclusion</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff record why the screen did not happen as discrete data rather than leaving it blank, and schedule a re-attempt, so that an absent result stays distinguishable from a negative one</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments; DC.2.3.1 Standard Assessments and Outcomes; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">11.2-2A</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyzer</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Auto-classify screening outcome (negative / non-acute positive / acute positive) and derive configurable risk tier</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening item responses; local stratification rules by setting/age; clinician override (if allowed)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Discrete screening outcome + risk tier with timestamp; reason/override metadata (if clinician overrides)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR applies configurable rules to derive an outcome/risk tier from screener responses and records the result as discrete data</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.1 Support for Standard Care Plans</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2B</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Status / Visibility Manager</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Communicate suicide screening status to the ED team (trackboard + chart banner)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening outcome/risk tier; patient context; local display rules</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Visible ED trackboard icon and/or chart banner indicator reflecting screening status; audit trail of status changes</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR displays a prominent indicator (separate from workflow tasking) so all ED roles can recognize current screening status at a glance</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="88" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2C</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CDS / Workflow Router</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Route protocol work via Tasks/advisories and provide one-click access to relevant order set/checklists</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening outcome/risk tier; local ED protocol rules; staffing/role assignments; patient location</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Role-routed Tasks/notifications (e.g., notify ED provider, initiate safety mitigation checklist, request BH consult, schedule BSSA when applicable); acceptance/override reason capture</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR creates role-based Tasks and, where configured, launches a staff advisory that links directly to the appropriate protocol order set/checklists</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Support for Standard Care Plans, Guidelines, Protocols; IN.5.1 Support Decision Logic</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.2-2D (proposed)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHR System</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Router</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close the loop on a negative screen</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negative screening outcome; local re-screen interval by setting and presentation; clinician override capability</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded negative result with instrument and timestamp; next re-screen due date; no protocol Tasks created; an escalation path that remains open to clinician judgment</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The EHR records the negative outcome, suppresses protocol tasking, sets the next re-screen interval, and keeps an explicit path for a clinician to escalate on judgment despite the negative result</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; IN.5.1 Support Decision Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scenario 11.3 – Immediate Safety / Mitigation
 For acute positive or otherwise high-risk presentations, the ED must rapidly mitigate environmental and procedural risks. The EHR supports a standardized mitigation checklist/order set, documents observation level and environmental safety actions, and ensures provider authorization/countersignature where required.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1A</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Nurse</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementer / Initiator</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Initiate immediate safety mitigation (keep patient in sight; move to room; start mitigation checklist)</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Positive screen/risk tier; local ED suicide safety protocol; current bed/room assignment</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Started mitigation checklist/Tasks; documentation that patient moved to a safer setting and not left unattended (when indicated)</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nurse initiates immediate mitigation per protocol and opens the mitigation checklist in the EHR to track required actions and handoffs</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Support for Standard Care Plans; DC.1.1.3 Manage Encounter Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="74" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1B</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ED Provider (MD/APP)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orderer / Authorizer</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Authorize and tailor suicide precaution / observation orders (with required signature/countersignature)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Risk tier; nursing mitigation status; local order set defaults; patient-specific medical needs (lines, monitoring, imaging, etc.)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signed orders for precautions (including observation level and parameters); ordered consults; order modifications with rationale</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provider reviews recommended protocol orders, tailors parameters to the patient, and signs/countersigns as required (EHR enforces role-based ordering and captures rationale for deviations)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.6.1 Order Entry; IN.2.2 Auditable Records</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1C</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ED Nurse / Tech / Security</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Safety Implementer</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Complete and document environmental safety / room clearance checklist and belongings security</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Room clearance checklist content; patient belongings inventory; local ligature/sharps risk guidance</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Completed checklist (time, performer, verifier); belongings secured record; exceptions documented with mitigation plan</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Team completes room clearance and belongings safety steps (remove/secure potentially harmful items, cords/tubing not needed for care, sharps containers, etc.) and documents completion in a structured checklist</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="88" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1D</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observer (Sitter)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Continuous Observer</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Begin continuous observation when indicated; document observations and safety checks</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation order/level; patient location; observer role assignment; documentation frequency rules</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation documentation record (time-stamped entries); observer identity/competency; handoff log</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A qualified observer provides continuous visual observation per policy when the patient is high-risk in an environment with safety hazards; the observer documents at the required interval and escalates concerns immediately</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
         </is>
       </c>
     </row>
     <row r="14" ht="74" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">11.3-1B</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ED Provider (MD/APP)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orderer / Authorizer</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Authorize and tailor suicide precaution / observation orders (with required signature/countersignature)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk tier; nursing mitigation status; local order set defaults; patient-specific medical needs (lines, monitoring, imaging, etc.)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Signed orders for precautions (including observation level and parameters); ordered consults; order modifications with rationale</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provider reviews recommended protocol orders, tailors parameters to the patient, and signs/countersigns as required (EHR enforces role-based ordering and captures rationale for deviations)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.6.1 Order Entry; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.3-1C</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ED Nurse / Tech / Security</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Implementer</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete and document environmental safety / room clearance checklist and belongings security</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Room clearance checklist content; patient belongings inventory; local ligature/sharps risk guidance</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed checklist (time, performer, verifier); belongings secured record; exceptions documented with mitigation plan</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team completes room clearance and belongings safety steps (remove/secure potentially harmful items, cords/tubing not needed for care, sharps containers, etc.) and documents completion in a structured checklist</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.3-1D</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observer (Sitter)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continuous Observer</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Begin continuous observation when indicated; document observations and safety checks</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation order/level; patient location; observer role assignment; documentation frequency rules</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation documentation record (time-stamped entries); observer identity/competency; handoff log</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A qualified observer provides continuous visual observation per policy when the patient is high-risk in an environment with safety hazards; the observer documents at the required interval and escalates concerns immediately</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">11.3-1E</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Status / Visibility Manager</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Persist and display active safety precautions (incl. observation level, checklist completion, and observer assignment)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Orders/Tasks for mitigation; completed checklist; observation order/level; observer assignment</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Active precaution status indicator (e.g., "Suicide precautions ON" + observation level) + checklist/observer status on trackboard/banner; audit trail</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR stores active precautions and their current parameters, displays them on ED views, and maintains an audit trail of when precautions were started/changed/ended</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scenario 11.4 – Brief Assessment and Suicide Risk Assessment
 After a positive screen, a trained clinician completes a brief suicide safety assessment (especially when ASQ is used and the screen is non-acute positive) to determine next steps. When indicated, the care team completes a structured suicide risk assessment (e.g., SAFE-T with C-SSRS). The EHR captures key assessment elements as discrete data and supports disposition decision-making.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="19" ht="88" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-0A</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Clinician / Behavioral Health Clinician</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assessor</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Complete Brief Suicide Safety Assessment (BSSA) after positive screen (as applicable)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening results (incl. acuity); relevant history; current presentation; collateral info when available</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Structured BSSA record (discrete elements + narrative) including frequency of suicidal thoughts, plan/intent, past behavior, symptoms, supports/stressors, and means access; recommended next step</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician completes a brief assessment to triage next steps (e.g., urgent full mental health evaluation vs proceed with ED discharge planning with interventions) and documents key elements as structured data</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="88" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20" ht="88" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-0B</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyzer / Router</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Record BSSA outcome and route next steps (full evaluation vs proceed to discharge pathway)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">BSSA findings; clinician determination; local clinical pathway rules</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Disposition routing Tasks (e.g., STAT mental health evaluation, BH consult); updated risk status indicator; documentation of "cannot leave until evaluated" status when applicable</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR persists the BSSA, updates ED-visible indicators, and triggers the next protocol stage based on the clinician's determination and local pathway rules</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.3 Care Plans Protocols</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="88" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-1A</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Behavioral Health Clinician</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assessor</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Complete structured suicide risk assessment (e.g., SAFE-T with C-SSRS) when indicated</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening + BSSA results (if performed); relevant prior history (prior attempts, diagnoses, substance use, meds); current presentation</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Structured risk assessment record (discrete elements + clinician narrative) including ideation severity, intent/plan, recent behavior, protective factors, and means access</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician completes a structured assessment in the EHR and documents key elements as discrete data to support risk determination and disposition planning</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22" ht="74" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-1B</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyzer / Persister</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Record suicide risk level/status and update ED-visible and longitudinal indicators</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Structured assessment data; clinician determination</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Discrete current suicide risk level/status (e.g., low/moderate/high/imminent) with timestamp; persistent risk indicator; optional coded diagnosis/problem entry</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR persists the risk level as a longitudinal data element, updates ED banner/trackboard indicators, and triggers downstream workflows per policy</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.3.1 Manage Alerts; DC.2.4 Manage Care Plans</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scenario 11.5 – Boarding and Reassessment
 When patients board in the ED awaiting psychiatric placement or transfer, risk status and precautions may change over time. The EHR supports time-based reassessment tasks (screening/assessment checkpoints), precaution updates, and continuity during handoffs across ED shifts.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="88" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1A</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task Scheduler</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Generate reassessment tasks/checkpoints while patient remains in ED (risk, precautions, environment, and observer status)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Time since last assessment; boarding status; observation level; last room clearance time; protocol rules by risk tier</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Scheduled reassessment Tasks (due time + responsible role); reminders/escalations; completion tracking</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR schedules reassessment checkpoints (e.g., every X hours, prior to shift change, or before disposition) and escalates if overdue; includes prompts for room re-sweep and observer/precaution review where required</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Care Plans Protocols; IN.5.1 Support Decision Logic</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="74" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="25" ht="74" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1B</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Clinician</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Reassessor</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Reassess suicide risk and update orders/precautions as clinically indicated</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Prior screening/assessment results; current symptoms; new events (agitation, elopement risk); protocol guidance</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Updated risk level/status (discrete); updated precaution orders/parameters; updated safety plan if appropriate</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician completes reassessment and updates risk status and precaution orders; EHR makes it easy to modify/discontinue/tailor orders while retaining prior values for audit/longitudinal tracking</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.3.1 Standard Assessments; DC.1.6.1 Order Entry</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="88" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1C</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Nurse / Charge Nurse</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety Monitor</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Re-check environmental safety (room clearance) and confirm observer assignment at shift change / room move</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Current room assignment; last room clearance checklist; observation order/level; staffing assignments</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Updated checklist record (if repeated); updated observer assignment/handoff log; exceptions documented</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">When the patient remains in the ED or changes rooms, staff repeat the environmental safety sweep per policy and confirm continuous observation coverage (if ordered), documenting completion and any exceptions</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5-1D (proposed)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ED Provider (MD/APP)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disposition Manager</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arrange psychiatric admission or transfer when ED discharge is not appropriate</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk determination; level of care needed and bed availability; receiving facility acceptance; authorization status; transport requirements; EMTALA obligations</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission or transfer order; accepting facility and clinician recorded; per-attempt placement log including refusals; transfer packet; transport arranged with precautions maintained en route</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The care team pursues placement, documents each attempt and refusal, records the accepting facility and clinician, and ensures precautions and observation continue through transport</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.6.1 Order Entry; DC.2.5 Order Entry — Referrals; IN.4 Manage Health Information Sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5-1E (proposed)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ED Nurse / Charge Nurse</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Monitor</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manage elopement or departure against advice by a patient at risk</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation status; last known location and time; risk tier; emergency contacts and any consent to contact them; local policy on notification and welfare checks</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time-stamped elopement event; escalation notifications; documented search and contact attempts; encounter disposition updated; crisis resources sent by a permitted channel where possible</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff escalate per policy, document the search and notification steps taken, update the encounter disposition, and attempt outreach with crisis resources rather than closing the encounter silently</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.1.3 Manage Encounter Information; DC.1.3.1 Manage Alerts; IN.5.1 Support Decision Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scenario 11.6 – Safety Planning and Discharge Planning
 Before ED discharge of a patient with suicide risk, best practice is to create or update a collaborative safety plan, provide lethal means counseling (a distinct intervention), and arrange rapid follow-up. The EHR supports structured, versioned safety plans; structured lethal means safety actions; and discharge-step completion with automatic inclusion/printing of required patient materials.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="74" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="30" ht="74" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1A</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Clinician</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Enterer</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Develop structured safety plan with patient prior to discharge</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Current suicide risk level/status; patient-identified warning signs, coping strategies, supports; crisis resources preferences</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Structured safety plan (versioned) including warning signs, internal coping, supports, professional/crisis resources (incl. 988), and follow-up contacts</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician collaborates with patient to complete a structured safety plan template and confirms preferred access method (print and/or portal)</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.7.1 Capture Standardized Assessments</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1B</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Retainer / Versioner</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Store, version, and make safety plan retrievable across settings</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Structured safety plan data</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Versioned safety plan stored in dedicated chart location; audit trail; linkage to risk status; patient-facing copy-ready artifact</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR persists and versions the safety plan; supports rapid retrieval for ED and downstream teams; retains prior versions with timestamps</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4 Manage Care Plans; IN.2.2 Auditable Records</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="74" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="32" ht="88" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-1C (proposed)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient (with support person, if present)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collaborator</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review, contribute to, and accept the safety plan</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draft safety plan; the patient's own words for warning signs and coping strategies; who the patient agrees may be named as a support; preferred delivery method and language</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient-confirmed safety plan with authorship attributed; recorded agreement to name each support person; chosen delivery method; declined elements recorded rather than omitted</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The patient reviews and revises the plan in their own words, confirms which supports may be named and contacted, and accepts or declines each element; declines are recorded so the next clinician knows what was already discussed</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.3.2 Support Patient Education and Self-Care; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="74" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2A</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Clinician</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Educator</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide lethal means counseling and document agreed actions (stand-alone intervention)</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Means access details (firearms, medications, other); patient/caregiver participants; agreed storage/removal plan</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Discrete lethal-means safety action plan (what/who/where/when) linked to encounter and/or safety plan; education/handout delivery record</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician provides lethal means counseling and documents agreed, time-bound means-safety actions; provides education materials and involves supports when appropriate</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.7 Patient Education; DC.2.4 Manage Care Plans</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2B</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Discharge Checklist Manager</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ensure ED discharge requirements are complete for patients with suicide risk</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Risk level/status; completion status of assessment, safety plan, lethal means counseling, and follow-up arrangements</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Discharge readiness checklist status; blocking alerts (if requirements incomplete); compiled AVS package</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR enforces (or strongly prompts) completion of required elements before discharge and compiles required documents into the AVS/after-visit packet</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.6.1 Order Entry; IN.5.1 Support Decision Logic</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="102" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-2C (proposed)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient and/or caregiver</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Means-Safety Participant</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commit to and carry out the agreed means-safety actions</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agreed storage or removal plan; who is responsible for each action; timeframe; caregiver availability; lock boxes, medication disposal, or off-site storage options</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named responsible party per action with a due date; confirmation as each action completes; barriers recorded; a follow-up Task for anything still outstanding at discharge</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The patient and any participating caregiver commit to specific, time-bound actions, and the EHR tracks each one to completion rather than recording only that counseling occurred</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7 Patient Education; DC.2.4 Manage Care Plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="102" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-3A</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Patient Materials Generator</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Auto-generate and auto-deliver/print safety plan and suicide-specific discharge instructions</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Final safety plan version; local crisis resource directory; patient language/reading level needs; follow-up appointments; patient preferred delivery (print/portal)</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Printed and/or portal-delivered safety plan copy; discharge instructions with psychoeducation and crisis resources; delivery/receipt documentation</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">At discharge, the EHR automatically includes the safety plan and suicide-specific discharge instructions (including crisis resources and local supports) in the AVS; prints and/or releases to portal per patient preference, and records that materials were delivered</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.9 Manage Patient Education; DC.2.7.2 Patient Discharge Summary</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="46" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="37" ht="116" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-3B (proposed)</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHR System</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Release Manager</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apply release and confidentiality rules before portal delivery</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient age and applicable minor-consent law; proxy or guardian portal access configuration; whether the safety plan names a support person or carries sensitive content; the patient's stated preference; sensitive-content suppression rules</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Release decision per document with the rule that produced it; suppressed or redacted items with a reason; an alternative delivery route where portal release is withheld; audit entry</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before the automatic release in 11.6-3A, the EHR evaluates who will actually be able to see each document — including a guardian holding proxy access — and withholds, redacts, or re-routes rather than releasing by default</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN.1.9 Manage Patient Privacy and Confidentiality; DC.1.9 Manage Patient Education; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Scenario 11.7 – Care Transitions and Follow-Up
 The EHR supports closed-loop care transitions from the ED by transmitting key suicide-related information (as permitted) to next providers, arranging rapid follow-up, and initiating post-discharge contacts (caring contacts and phone follow-up) with monitoring and escalation.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-0A (proposed)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ED Clinician</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consent and Privacy Manager</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capture consent and privacy directives before any disclosure</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient or guardian authorization preferences; applicability of 42 CFR Part 2 and state minor-consent law; emergency-exception provisions; which categories of information may go to which recipients</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consent record with scope, recipients, and expiry; recorded basis where disclosure proceeds under an emergency exception; restrictions attached to the transition packet and to follow-up outreach</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The clinician records what the patient authorizes, to whom, and for how long, before 11.7-1B assembles a packet; where an emergency exception is relied on instead, the basis for it is recorded as discrete data</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN.1.9 Manage Patient Privacy and Confidentiality; IN.4 Manage Health Information Sharing; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-1A</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED Clinician</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Orderer</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Place urgent outpatient follow-up / referral and document disposition plan</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Risk level/status; patient preferences; referral destination; consent/privacy directives</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Referral/AppointmentRequest with urgency; discharge disposition plan; tasks for outreach and follow-up</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinician places an urgent follow-up request/referral and documents disposition plan, including timeframe and responsible role for scheduling/outreach</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.5 Order Entry — Referrals; DC.1.6.1 Order Entry</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-1B</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Transmitter / Care Transition Packager</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Generate and transmit ED transition-of-care packet</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening/assessment outputs; safety plan; lethal-means action plan; demographics; consent/privacy directives</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Transition-of-care packet (electronic); notifications to receiving providers; delivery acknowledgements (when available)</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR packages and transmits relevant structured information; notifies receiving providers and stores delivery status/acknowledgements when supported</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.7.1 Care Plan, Guideline, Protocol Generation; IN.4 Manage Health Information Sharing</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2A</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up Protocol Manager</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Initiate post-discharge follow-up protocol (caring contacts and phone calls)</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ED discharge event; risk tier; configured follow-up rules and cadence; patient contact info</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-up Task set (e.g., 24–48h call, 7-day visit); caring contacts schedule; registry/dashboard enrollment</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR generates protocol-driven follow-up tasks, schedules caring contacts, enrolls patient in a registry/dashboard, and tracks completion and outcomes</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Care Plans Protocols; DC.2.4 Manage Care Plans</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2B</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Care Team</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Outreach / Monitor</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Conduct follow-up outreach and document outcomes</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assigned follow-up tasks; patient contact information; safety plan; current risk status</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Outreach documentation; updated risk status (as needed); updated safety plan; next scheduled follow-up</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Care team completes outreach per protocol, documents outcomes, updates risk status/safety plan as needed, and schedules next steps</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="74" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="44" ht="74" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2C</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR System</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Exception / Escalation Manager</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Detect missed follow-up and escalate care coordination</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task status; no-response indicators; missed appointment status; escalation rules</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Escalation alerts; reassigned tasks; documentation of attempted contacts; updated registry status</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">EHR detects overdue tasks or missed appointments for elevated-risk patients and escalates per protocol (e.g., supervisor alert, additional outreach, welfare check guidance)</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">IN.5.1 Support Decision Logic; DC.1.3.1 Manage Alerts</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="74" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-2D (proposed)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient (or caregiver)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Participant</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respond to post-discharge outreach, or not</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outreach attempt on the consented channel; safety plan in hand; current supports and stressors</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Response state recorded (reached, no answer, declined further contact, consent withdrawn); patient-reported status; updated channel preference</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The patient engages with the caring contact or follow-up call; the EHR records non-response and withdrawal as states distinct from "not attempted", which is what 11.7-2C escalates on</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
         </is>
       </c>
     </row>
@@ -1339,11 +1759,11 @@
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A38:H38"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1352,14 +1772,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12"/>
+    <col customWidth="1" min="1" max="1" width="16"/>
     <col customWidth="1" min="2" max="2" width="26"/>
     <col customWidth="1" min="3" max="3" width="34"/>
     <col customWidth="1" min="4" max="4" width="40"/>
     <col customWidth="1" min="5" max="5" width="11"/>
     <col customWidth="1" min="6" max="6" width="20"/>
     <col customWidth="1" min="7" max="7" width="22"/>
-    <col customWidth="1" min="8" max="8" width="46"/>
+    <col customWidth="1" min="8" max="8" width="40"/>
+    <col customWidth="1" min="9" max="9" width="52"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1403,6 +1824,11 @@
           <t xml:space="preserve">Review notes</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed — rationale</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -1468,25 +1894,25 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="46" customHeight="1">
+    <row r="4" ht="74" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.2-2A</t>
+          <t xml:space="preserve">11.2-1C (proposed)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation</t>
+          <t xml:space="preserve">QuestionnaireResponse; Patient; Provenance</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — needs a SPiER ASQ Outcome Observation profile (low/non-acute positive/acute positive)</t>
+          <t xml:space="preserve">Reuses the ASQ / C-SSRS Screener Questionnaires (11.2-1A); gap — no convention yet for self-report authorship</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.1 Support for Standard Care Plans</t>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments; DC.3.2 Support Patient Education and Self-Care</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1494,36 +1920,36 @@
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-view</t>
-        </is>
-      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-2a</t>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The scenario permits patient self-report in 11.2-1A but never gives the patient an Actor row, so nothing distinguishes a self-completed screen — including whether the patient was alone when answering, which changes how the answers should be read.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.2-2B</t>
+          <t xml:space="preserve">11.2-1D (proposed)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flag</t>
+          <t xml:space="preserve">QuestionnaireResponse; Observation; Task</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — SPiER Suicide-Screening-Status Flag profile</t>
+          <t xml:space="preserve">gap — Screening-Not-Performed Observation with a coded reason, and the convention separating it from a negative screen</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments; DC.2.3.1 Standard Assessments and Outcomes; IN.2.2 Auditable Records</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1533,236 +1959,251 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-2b</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kelly Samuelson (2026-02-19, event): storyboard - need the vendor agnostic version of this and then EHR specialist can translate this per EHR</t>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A blank is currently indistinguishable from a negative screen. That difference drives both the clinical follow-up and the denominator of every screening measure.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">11.2-2A</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — needs a SPiER ASQ Outcome Observation profile (low/non-acute positive/acute positive)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.1 Support for Standard Care Plans</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-view</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-2-2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.2-2B</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flag</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — SPiER Suicide-Screening-Status Flag profile</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-2-2b</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kelly Samuelson (2026-02-19, event): storyboard - need the vendor agnostic version of this and then EHR specialist can translate this per EHR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">11.2-2C</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task; ServiceRequest; PlanDefinition</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">SPiER PlanDefinition for stage-1 → stage-2 transition (pathway-stages.fsh)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Support for Standard Care Plans, Guidelines, Protocols; IN.5.1 Support Decision Logic</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">built</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">order-select / advisory</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-2-2c</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.2-2D (proposed)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation; Task</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reuses the screening outcome Observation (11.2-2A); gap — negative-result handling and re-screen interval are unspecified</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; IN.5.1 Support Decision Logic</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.2-2A defines three outcomes but only the positive ones are consumed anywhere. A negative screen still has consequences: a re-screen interval, and the standing ability of a clinician to escalate anyway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1A</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task; Procedure</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Mitigation Checklist Task profile</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Support for Standard Care Plans; DC.1.1.3 Manage Encounter Information</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-3-1a</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1B</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ServiceRequest</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Suicide Precaution ServiceRequest profile</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.6.1 Order Entry; IN.2.2 Auditable Records</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">order-sign</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-3-1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1C</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation; List</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Room Clearance Checklist profile; Belongings Inventory profile</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1D</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation; CareTeam</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Continuous Observation Log profile</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="74" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.3-1E</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flag</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Active Precautions Flag profile</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">not narrated — The demo emits no Flag resource, so there is no active-precautions indicator to narrate.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.4-0A</t>
+          <t xml:space="preserve">11.3-1C</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse</t>
+          <t xml:space="preserve">Observation; List</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — needs FSH for BSSA (TL-005, status:planned, promote priority)</t>
+          <t xml:space="preserve">gap — Room Clearance Checklist profile; Belongings Inventory profile</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
+          <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1772,29 +2213,29 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-4-0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="88" customHeight="1">
+          <t xml:space="preserve">patient-011 / ed-11-3-1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.4-0B</t>
+          <t xml:space="preserve">11.3-1D</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observation; Task; Flag</t>
+          <t xml:space="preserve">Observation; CareTeam</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — BSSA Outcome Observation; "Hold for Evaluation" Flag</t>
+          <t xml:space="preserve">gap — Continuous Observation Log profile</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.3 Care Plans Protocols</t>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1802,504 +2243,859 @@
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-view</t>
-        </is>
-      </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — The demo records the BSSA (11.4-0A) but emits no routing Task, so there is no artifact for this step.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
+          <t xml:space="preserve">patient-011 / ed-11-3-1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="74" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.4-1A</t>
+          <t xml:space="preserve">11.3-1E</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuestionnaireResponse</t>
+          <t xml:space="preserve">Flag</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-SSRS Full (built — cssrs-full-lifetime-recent.json); SAFE-T (TL-006, status:planned, promote)</t>
+          <t xml:space="preserve">gap — Active Precautions Flag profile</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
+          <t xml:space="preserve">DC.1.3.1 Manage Alerts; IN.5 Clinical Decision Support</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">built</t>
+          <t xml:space="preserve">gap</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-4-1a</t>
+          <t xml:space="preserve">not narrated — The demo emits no Flag resource, so there is no active-precautions indicator to narrate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">11.4-0A</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — needs FSH for BSSA (TL-005, status:planned, promote priority)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-4-0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.4-0B</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation; Task; Flag</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — BSSA Outcome Observation; "Hold for Evaluation" Flag</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.3 Care Plans Protocols</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-view</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — The demo records the BSSA (11.4-0A) but emits no routing Task, so there is no artifact for this step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.4-1A</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-SSRS Full (built — cssrs-full-lifetime-recent.json); SAFE-T (TL-006, status:planned, promote)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7.1 Capture Standardized Assessments</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">built</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-4-1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">11.4-1B</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Observation; Condition; Flag</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Current Suicide Risk Level Observation; Longitudinal Risk Flag</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.3.1 Manage Alerts; DC.2.4 Manage Care Plans</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-4-1b</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1A</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task; PlanDefinition</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Reassessment Cadence PlanDefinition + Reassessment Task profile</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4.3 Care Plans Protocols; IN.5.1 Support Decision Logic</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-5-1a</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1B</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Observation; ServiceRequest</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Reuses Current Suicide Risk Level Observation (11.4-1B) + Suicide Precaution ServiceRequest (11.3-1B)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.3.1 Standard Assessments; DC.1.6.1 Order Entry</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">built</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-5-1b</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="74" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="21" ht="74" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1C</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CareTeam</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Reuses 11.3-1C and 11.3-1D profiles</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.6.2 Order Documents and Reports</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">built</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">not narrated — The demo has a single room-clearance event and no shift-change repeat.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="22" ht="74" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5-1D (proposed)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServiceRequest; Encounter; Organization; Communication</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Psychiatric Admission/Transfer Disposition profile, including the per-attempt placement log</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.6.1 Order Entry; DC.2.5 Order Entry — Referrals; IN.4 Manage Health Information Sharing</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5's own preamble describes patients awaiting psychiatric placement or transfer, but every step after it follows the discharge-home branch. The placement itself — and the log of failed attempts that explains a long boarding stay — is unmodelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="74" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.5-1E (proposed)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Encounter; Flag; Communication; Task</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Elopement / left-against-advice handling for an at-risk patient, including the notification and outreach chain</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.1.3 Manage Encounter Information; DC.1.3.1 Manage Alerts; IN.5.1 Support Decision Logic</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A patient on suicide precautions who leaves is among the highest-risk events an ED sees, and the scenario has no path for it. With no modelled event the encounter simply closes, and the follow-up protocol in 11.7 never fires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1A</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">QuestionnaireResponse; CarePlan</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Stanley-Brown (built)</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.7.1 Capture Standardized Assessments</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">built</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-6-1a</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-1B</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CarePlan; Provenance</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Reuses Stanley-Brown CarePlan profile; gap — versioning extension</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.2.4 Manage Care Plans; IN.2.2 Auditable Records</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-6-1b</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-1C (proposed)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CarePlan; Provenance; RelatedPerson</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reuses the Stanley-Brown CarePlan (11.6-1A); gap — patient authorship and per-element accept/decline are unmodelled</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.3.2 Support Patient Education and Self-Care; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The scenario calls the plan collaborative but models only the clinician side. A safety plan the patient did not actually agree to is a documented artifact rather than an intervention — and naming a support person the patient has not agreed to name is itself a disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2A</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Procedure; CarePlan</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Lethal Means Counseling Procedure + Means-Safety Action profile (TL-008, status:planned, promote)</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DC.1.7 Patient Education; DC.2.4 Manage Care Plans</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-6-2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.6-2B</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task; Flag</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Discharge Readiness Checklist profile</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.6.1 Order Entry; IN.5.1 Support Decision Logic</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">encounter-discharge</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.6-3A</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Composition; DocumentReference</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Suicide-Specific Discharge AVS Composition profile</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.1.9 Manage Patient Education; DC.2.7.2 Patient Discharge Summary</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.7-1A</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ServiceRequest; Appointment; Communication</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Urgent BH Follow-Up Referral profile (TL-009 Transition, status:planned, promote)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.5 Order Entry — Referrals; DC.1.6.1 Order Entry</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order-select</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.7-1B</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bundle; Composition; Provenance</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Suicide-Specific Transition-of-Care Bundle profile</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.7.1 Care Plan, Guideline, Protocol Generation; IN.4 Manage Health Information Sharing</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="144" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.7-2A</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Task; CommunicationRequest; Communication; PlanDefinition</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — Caring Contacts PlanDefinition + Caring Contact Task profile (TL-010, status:planned, promote); ED-SAFE telephone follow-up profile (TL-012, status:planned, promote) — ED-SAFE specifies the phone-call protocol that Caring Contacts envelopes; both are needed for an ED-anchored follow-up program</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.4.3 Care Plans Protocols; DC.2.4 Manage Care Plans</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.7-2B</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Communication; Observation; CarePlan</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reuses earlier profiles</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">built</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2b</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">11.6-2B</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task; Flag</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Discharge Readiness Checklist profile</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.6.1 Order Entry; IN.5.1 Support Decision Logic</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">encounter-discharge</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-6-2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="74" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-2C (proposed)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CarePlan; RelatedPerson; Task</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Means-safety actions need a responsible party, a due date, and a completion state, not just a counseling record</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.7 Patient Education; DC.2.4 Manage Care Plans</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-2A documents that counseling happened and what was agreed, but nothing owns the actions or closes them out. Means-safety is the intervention with the strongest evidence base here, and "agreed" is not "done".</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-3A</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Composition; DocumentReference</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Suicide-Specific Discharge AVS Composition profile</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.1.9 Manage Patient Education; DC.2.7.2 Patient Discharge Summary</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-6-3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="88" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.6-3B (proposed)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DocumentReference; Consent</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Release / confidentiality rule evaluation, including adolescent proxy access</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN.1.9 Manage Patient Privacy and Confidentiality; DC.1.9 Manage Patient Education; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For an adolescent whose guardian holds proxy access, or a plan naming a member of the household the patient is unsafe with, automatic portal release can be the harm. Real deployments gate this, and the scenario should say so rather than describing release as automatic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="74" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-0A (proposed)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consent; Provenance</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Suicide-Care Disclosure Consent profile, covering Part 2 programs, minor consent, and the emergency exception</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN.1.9 Manage Patient Privacy and Confidentiality; IN.4 Manage Health Information Sharing; IN.2.2 Auditable Records</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consent appears only as an input to 11.7-1A and 11.7-1B. Whether the packet may lawfully be sent is a decision with an actor, a timestamp, and a record — and for a minor or a Part 2 program it can forbid the transmission the scenario assumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-1A</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ServiceRequest; Appointment; Communication</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Urgent BH Follow-Up Referral profile (TL-009 Transition, status:planned, promote)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.5 Order Entry — Referrals; DC.1.6.1 Order Entry</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order-select</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-7-1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-1B</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundle; Composition; Provenance</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Suicide-Specific Transition-of-Care Bundle profile</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.7.1 Care Plan, Guideline, Protocol Generation; IN.4 Manage Health Information Sharing</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-7-1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="144" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-2A</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task; CommunicationRequest; Communication; PlanDefinition</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Caring Contacts PlanDefinition + Caring Contact Task profile (TL-010, status:planned, promote); ED-SAFE telephone follow-up profile (TL-012, status:planned, promote) — ED-SAFE specifies the phone-call protocol that Caring Contacts envelopes; both are needed for an ED-anchored follow-up program</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4.3 Care Plans Protocols; DC.2.4 Manage Care Plans</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-7-2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-2B</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Communication; Observation; CarePlan</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reuses earlier profiles</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">built</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011 / ed-11-7-2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">11.7-2C</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Task; Communication; Flag</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap — Follow-Up Overdue Escalation profile</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">IN.5.1 Support Decision Logic; DC.1.3.1 Manage Alerts</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-011 / ed-11-7-2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-2D (proposed)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Communication; Consent</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap — Outreach response states distinguishing no-answer, declined, and withdrawn</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.4 Manage Care Plans; DC.1.3.1 Manage Alerts</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gap</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.7-2C escalates on missed follow-up, but nothing models the patient side of the contact. "No answer" and "asked us to stop" are clinically and legally different, and only one of them should escalate.</t>
         </is>
       </c>
     </row>

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -1894,7 +1894,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="74" customHeight="1">
+    <row r="4" ht="130" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1C (proposed)</t>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria was screened by the triage nurse (11.2-1A), so there is no self-completed screen to narrate. Needs a second ED patient.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="102" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1D (proposed)</t>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria completed the screener. Needs a second ED patient whose screen is declined or incompletable.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="102" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2D (proposed)</t>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria screened non-acute positive. Needs a second ED patient who screens negative.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="74" customHeight="1">
+    <row r="22" ht="102" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1D (proposed)</t>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria was discharged home with follow-up. Needs a second ED patient who is admitted or transferred.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="74" customHeight="1">
+    <row r="23" ht="102" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1E (proposed)</t>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria completed her ED care. Needs a second ED patient who elopes or leaves against advice.</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">patient-011 / ed-11-6-1c</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">patient-011 / ed-11-6-2c</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">patient-011 / ed-11-6-3b</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">patient-011 / ed-11-7-0a</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Proposed step; the demo does not narrate it yet.</t>
+          <t xml:space="preserve">patient-011 / ed-11-7-2d</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -1830,7 +1830,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="88" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1A</t>
@@ -1858,11 +1858,13 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="102" customHeight="1">
+          <t xml:space="preserve">patient-011/ed-11-2-1a
+patient-013/ed13-11-2-1a
+patient-014/ed14-11-2-1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1B</t>
@@ -1890,11 +1892,11 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Persistence has no separate narration in the demo: the QuestionnaireResponse referenced by 11.2-1A is the persisted resource.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="130" customHeight="1">
+          <t xml:space="preserve">patient-012/ed12-11-2-1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="74" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1C (proposed)</t>
@@ -1922,7 +1924,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria was screened by the triage nurse (11.2-1A), so there is no self-completed screen to narrate. Needs a second ED patient.</t>
+          <t xml:space="preserve">patient-012/ed12-11-2-1c</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -1931,7 +1933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="102" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1D (proposed)</t>
@@ -1959,7 +1961,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria completed the screener. Needs a second ED patient whose screen is declined or incompletable.</t>
+          <t xml:space="preserve">patient-013/ed13-11-2-1d</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -1968,7 +1970,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2A</t>
@@ -2001,7 +2003,9 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-2a</t>
+          <t xml:space="preserve">patient-011/ed-11-2-2a
+patient-012/ed12-11-2-2a
+patient-013/ed13-11-2-2a</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2037,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-2b</t>
+          <t xml:space="preserve">patient-011/ed-11-2-2b</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -2075,11 +2079,11 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-2-2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="102" customHeight="1">
+          <t xml:space="preserve">patient-011/ed-11-2-2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2D (proposed)</t>
@@ -2107,7 +2111,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria screened non-acute positive. Needs a second ED patient who screens negative.</t>
+          <t xml:space="preserve">patient-012/ed12-11-2-2d</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -2144,7 +2148,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1a</t>
+          <t xml:space="preserve">patient-011/ed-11-3-1a</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2185,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1b</t>
+          <t xml:space="preserve">patient-011/ed-11-3-1b</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1c</t>
+          <t xml:space="preserve">patient-011/ed-11-3-1c</t>
         </is>
       </c>
     </row>
@@ -2245,11 +2249,11 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-3-1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="74" customHeight="1">
+          <t xml:space="preserve">patient-011/ed-11-3-1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.3-1E</t>
@@ -2277,7 +2281,8 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — The demo emits no Flag resource, so there is no active-precautions indicator to narrate.</t>
+          <t xml:space="preserve">patient-013/ed13-11-3-1e
+patient-014/ed14-11-3-1e</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2314,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-4-0a</t>
+          <t xml:space="preserve">patient-011/ed-11-4-0a</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2351,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — The demo records the BSSA (11.4-0A) but emits no routing Task, so there is no artifact for this step.</t>
+          <t xml:space="preserve">not-narrated — The demo records the BSSA (11.4-0A) but emits no routing Task, so there is no artifact for this step.</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2383,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-4-1a</t>
+          <t xml:space="preserve">patient-011/ed-11-4-1a</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2415,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-4-1b</t>
+          <t xml:space="preserve">patient-011/ed-11-4-1b</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2447,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-5-1a</t>
+          <t xml:space="preserve">patient-011/ed-11-5-1a</t>
         </is>
       </c>
     </row>
@@ -2474,11 +2479,11 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-5-1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="74" customHeight="1">
+          <t xml:space="preserve">patient-011/ed-11-5-1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1C</t>
@@ -2506,11 +2511,11 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — The demo has a single room-clearance event and no shift-change repeat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="102" customHeight="1">
+          <t xml:space="preserve">patient-014/ed14-11-5-1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="74" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1D (proposed)</t>
@@ -2538,7 +2543,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria was discharged home with follow-up. Needs a second ED patient who is admitted or transferred.</t>
+          <t xml:space="preserve">patient-013/ed13-11-5-1d</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2547,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="102" customHeight="1">
+    <row r="23" ht="74" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1E (proposed)</t>
@@ -2575,7 +2580,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not narrated — Branch-exclusive on patient-011: Maria completed her ED care. Needs a second ED patient who elopes or leaves against advice.</t>
+          <t xml:space="preserve">patient-014/ed14-11-5-1e</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2612,7 +2617,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-1a</t>
+          <t xml:space="preserve">patient-011/ed-11-6-1a</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2649,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-1b</t>
+          <t xml:space="preserve">patient-011/ed-11-6-1b</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2681,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-1c</t>
+          <t xml:space="preserve">patient-011/ed-11-6-1c</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2713,7 +2718,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-2a</t>
+          <t xml:space="preserve">patient-011/ed-11-6-2a</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2755,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-2b</t>
+          <t xml:space="preserve">patient-011/ed-11-6-2b</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2787,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-2c</t>
+          <t xml:space="preserve">patient-011/ed-11-6-2c</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2819,7 +2824,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-3a</t>
+          <t xml:space="preserve">patient-011/ed-11-6-3a</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2856,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-6-3b</t>
+          <t xml:space="preserve">patient-011/ed-11-6-3b</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2888,7 +2893,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-0a</t>
+          <t xml:space="preserve">patient-011/ed-11-7-0a</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2930,7 +2935,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-1a</t>
+          <t xml:space="preserve">patient-011/ed-11-7-1a</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2967,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-1b</t>
+          <t xml:space="preserve">patient-011/ed-11-7-1b</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2999,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2a</t>
+          <t xml:space="preserve">patient-011/ed-11-7-2a</t>
         </is>
       </c>
     </row>
@@ -3026,11 +3031,11 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
+          <t xml:space="preserve">patient-011/ed-11-7-2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2C</t>
@@ -3058,7 +3063,8 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2c</t>
+          <t xml:space="preserve">patient-011/ed-11-7-2c
+patient-014/ed14-11-7-2c</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3096,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient-011 / ed-11-7-2d</t>
+          <t xml:space="preserve">patient-011/ed-11-7-2d</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -2318,7 +2318,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-0B</t>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">not-narrated — The demo records the BSSA (11.4-0A) but emits no routing Task, so there is no artifact for this step.</t>
+          <t xml:space="preserve">patient-011/ed-11-4-0b</t>
         </is>
       </c>
     </row>

--- a/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
+++ b/docs/use-cases/dist/HL7_BH_USE_CASES-ED-Scenario-11.xlsx
@@ -1933,7 +1933,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="116" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-1D (proposed)</t>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Screening-Not-Performed Observation with a coded reason, and the convention separating it from a negative screen</t>
+          <t xml:space="preserve">Demonstrated with native Observation.dataAbsentReason (HL7 temp-unknown) on the risk-concept Observation — see p013-screen-not-done; gap — the convention is not profiled or written down, so nothing stops a site recording a deferral as a negative screen</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — needs a SPiER ASQ Outcome Observation profile (low/non-acute positive/acute positive)</t>
+          <t xml:space="preserve">SPiER ASQ Screening Result Observation (built — spier-asq-result), valued from the ASQ screening-result CodeSystem (negative / non-acute-positive / acute-positive)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="88" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.2-2B</t>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — SPiER Suicide-Screening-Status Flag profile</t>
+          <t xml:space="preserve">SPiER Suicide-Risk Flag (built) is the adjacent artifact, but it is deliberately the *episode* banner and carries no clinical detail; gap — a screening-status flag distinct from it</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
+    <row r="15" ht="74" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-0A</t>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — needs FSH for BSSA (TL-005, status:planned, promote priority)</t>
+          <t xml:space="preserve">SPiER BSSA Questionnaire (built) + AdministerBSSA ActivityDefinition (built) — TL-005 is built and launchable at /patient/assessments/bssa</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2309,41 +2309,41 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">built</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient-011/ed-11-4-0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.4-0B</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observation; Task; Flag</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPiER BSSA Disposition Result Observation (built — spier-bssa-disposition-result); gap — the "Hold for Evaluation" Flag</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.3 Care Plans Protocols</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">gap</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient-011/ed-11-4-0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11.4-0B</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation; Task; Flag</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap — BSSA Outcome Observation; "Hold for Evaluation" Flag</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC.2.3.1 Standard Assessments and Outcomes; DC.2.4.3 Care Plans Protocols</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gap</t>
-        </is>
-      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient-view</t>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="46" customHeight="1">
+    <row r="17" ht="74" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-1A</t>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-SSRS Full (built — cssrs-full-lifetime-recent.json); SAFE-T (TL-006, status:planned, promote)</t>
+          <t xml:space="preserve">C-SSRS Full (built — cssrs-full-lifetime-recent.json); SAFE-T (built — safet-questionnaire.json) — TL-006 is built and launchable at /patient/assessments/safe-t</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.4-1B</t>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Current Suicide Risk Level Observation; Longitudinal Risk Flag</t>
+          <t xml:space="preserve">SPiER Suicide Risk Concept Observation (built — spier-suicide-risk-concept) carrying the risk tier; SPiER Suicide-Risk Flag (built — spier-suicide-risk-flag) as the longitudinal chart banner</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1A</t>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Reassessment Cadence PlanDefinition + Reassessment Task profile</t>
+          <t xml:space="preserve">SPiER Reassessment Schedule PlanDefinition (built) + SPiER Safety Task (built — spier-safety-task, Task.code = reassessment-due)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="74" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.5-1D (proposed)</t>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Psychiatric Admission/Transfer Disposition profile, including the per-attempt placement log</t>
+          <t xml:space="preserve">Encounter.hospitalization.dischargeDisposition carries the transfer itself (psy), and the lethal-means measure now reads it as a denominator exception; gap — the per-attempt placement log</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="102" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2A</t>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Lethal Means Counseling Procedure + Means-Safety Action profile (TL-008, status:planned, promote)</t>
+          <t xml:space="preserve">SPiER Lethal Means Safety Counseling Procedure (built — spier-lethal-means-counseling) + SPiER Means Safety Action Observation (built — spier-means-safety-action) — TL-008 is built and launchable at /patient/workflow/lethal-means</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="74" customHeight="1">
+    <row r="29" ht="116" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-2C (proposed)</t>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Means-safety actions need a responsible party, a due date, and a completion state, not just a counseling record</t>
+          <t xml:space="preserve">SPiER Means Safety Action Observation (built) carries the completion state (status final = done, preliminary = agreed); gap — the responsible party and due date are narrative note text, not discrete elements, so neither is queryable or reportable</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
+    <row r="30" ht="74" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.6-3A</t>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Suicide-Specific Discharge AVS Composition profile</t>
+          <t xml:space="preserve">SPiER Discharge Safety Packet DocumentReference (built — spier-discharge-safety-packet) carries the packet and its content items; gap — the AVS Composition itself</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="74" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-0A (proposed)</t>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Suicide-Care Disclosure Consent profile, covering Part 2 programs, minor consent, and the emergency exception</t>
+          <t xml:space="preserve">SPiER Suicide-Safety Information-Sharing Consent (built — spier-information-sharing-consent) carries permit/deny, the named recipient and the period; gap — the legal-basis specifics</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="46" customHeight="1">
+    <row r="33" ht="130" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-1A</t>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Urgent BH Follow-Up Referral profile (TL-009 Transition, status:planned, promote)</t>
+          <t xml:space="preserve">SPiER Suicide-Safety Referral ServiceRequest (built — spier-safety-referral) + SPiER Follow-Up Appointment (built — spier-follow-up-appointment) + SPiER Suicide-Safety Handoff Communication (built — spier-safety-handoff) — TL-009 is built and launchable at /patient/workflow/transition</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="144" customHeight="1">
+    <row r="35" ht="116" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2A</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Caring Contacts PlanDefinition + Caring Contact Task profile (TL-010, status:planned, promote); ED-SAFE telephone follow-up profile (TL-012, status:planned, promote) — ED-SAFE specifies the phone-call protocol that Caring Contacts envelopes; both are needed for an ED-anchored follow-up program</t>
+          <t xml:space="preserve">SPiER Caring Contact (built — spier-caring-contact) — TL-010 is built and launchable at /patient/workflow/caring-contact; gap — no PlanDefinition schedules the series, and the ED-SAFE telephone protocol (TL-012) it would envelope is not modelled</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="102" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2C</t>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Follow-Up Overdue Escalation profile</t>
+          <t xml:space="preserve">SPiER Safety Task (built — spier-safety-task) with the escalation-trigger extension (spier-escalation-trigger), whose codes include missed-follow-up, missed-outreach-window and failed-contact-sequence</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="158" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">11.7-2D (proposed)</t>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap — Outreach response states distinguishing no-answer, declined, and withdrawn</t>
+          <t xml:space="preserve">SPiER Follow-Up Outreach Attempt (built — spier-outreach-attempt) with the outreach-outcome extension (spier-outreach-outcome: patient-reached, no-answer, message-left, unable-to-reach, wrong-contact-info, patient-declined, reached-support-person); a withdrawal of consent is a deny provision on the SPiER Information-Sharing Consent (built)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gap</t>
+          <t xml:space="preserve">built</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
